--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/coquimbo.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/coquimbo.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7722.58</v>
+        <v>7764.17</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3130.78</v>
+        <v>3123.05</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5137.35</v>
+        <v>5197.61</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>35961.44</v>
+        <v>36383.29</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12875.56</v>
+        <v>13093.32</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8234.34</v>
+        <v>8192.629999999999</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4315.43</v>
+        <v>4306.04</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/coquimbo.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/coquimbo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -938,6 +938,67 @@
         <v>4306.04</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1057439-5313-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.606.402-9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>10822.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/coquimbo.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -997,6 +997,189 @@
       </c>
       <c r="M9" s="2" t="n">
         <v>10822.92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1057439-5807-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.606.402-9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>11422.96</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1242131-981-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.606.404-5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>2586.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1242131-1226-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.606.404-5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>2305.97</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/coquimbo.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/coquimbo.xlsx
@@ -562,7 +562,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/coquimbo.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1208,6 +1208,136 @@
       </c>
       <c r="M12" s="2" t="n">
         <v>2305.97</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1057439-6644-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.606.402-9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>7952.33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1242131-1284-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.606.404-5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>2532.44</v>
       </c>
     </row>
   </sheetData>
